--- a/Programs/A3ASM/GT_Aufgabe_Woche_3_Speicher.xlsx
+++ b/Programs/A3ASM/GT_Aufgabe_Woche_3_Speicher.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DuyTrinh\Desktop\HawStudium\Semester 1\Grundlagen der technischen Informatik\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DuyTrinh\Desktop\GitProjekte\ITS-BRD-VSC\Programs\A3ASM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F56608-C7DD-4C0D-9383-8295056B80EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD6ABA7-C756-42E7-8807-2F9ABFD1BC0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2F3BCCD5-4B63-4AFE-B627-FCE26E36F91B}"/>
   </bookViews>
@@ -199,7 +199,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -238,7 +238,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7030A0"/>
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -270,7 +288,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -298,11 +316,23 @@
     <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -738,10 +768,10 @@
       <c r="K8" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="M8" s="13" t="s">
         <v>25</v>
       </c>
       <c r="N8" s="9" t="s">
@@ -750,10 +780,10 @@
       <c r="O8" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="P8" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="Q8" s="9" t="s">
+      <c r="Q8" s="13" t="s">
         <v>25</v>
       </c>
     </row>
@@ -767,16 +797,16 @@
       <c r="C9" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="13">
         <v>45</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="10" t="s">
+      <c r="E9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="12" t="s">
         <v>29</v>
       </c>
       <c r="H9" s="10" t="s">
@@ -785,10 +815,10 @@
       <c r="I9" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="10" t="s">
+      <c r="J9" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="12" t="s">
         <v>34</v>
       </c>
       <c r="L9" s="10" t="s">
@@ -797,10 +827,10 @@
       <c r="M9" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="O9" s="10" t="s">
+      <c r="N9" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="O9" s="12" t="s">
         <v>25</v>
       </c>
       <c r="P9" s="10" t="s">
@@ -820,10 +850,10 @@
       <c r="C10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="10" t="s">
+      <c r="D10" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F10" s="10" t="s">
@@ -832,10 +862,10 @@
       <c r="G10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="10" t="s">
+      <c r="H10" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="12" t="s">
         <v>32</v>
       </c>
       <c r="J10" s="10" t="s">
@@ -844,22 +874,22 @@
       <c r="K10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="M10" s="10" t="s">
+      <c r="L10" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="N10" s="13" t="s">
+      <c r="N10" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="O10" s="13" t="s">
+      <c r="O10" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="P10" s="13" t="s">
+      <c r="P10" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="Q10" s="13" t="s">
+      <c r="Q10" s="16" t="s">
         <v>42</v>
       </c>
     </row>
@@ -867,19 +897,19 @@
       <c r="A11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="15" t="s">
         <v>25</v>
       </c>
       <c r="G11" s="3" t="s">
@@ -917,7 +947,7 @@
       </c>
     </row>
     <row r="17" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H17" s="12"/>
+      <c r="H17" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
